--- a/output/学生成绩达成度分析.xlsx
+++ b/output/学生成绩达成度分析.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="28" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="7">
   <si>
     <t>考勤</t>
   </si>

--- a/output/学生成绩达成度分析.xlsx
+++ b/output/学生成绩达成度分析.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="77" uniqueCount="7">
   <si>
     <t>考勤</t>
   </si>

--- a/output/学生成绩达成度分析.xlsx
+++ b/output/学生成绩达成度分析.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="172" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="430" uniqueCount="13">
   <si>
     <t>考勤</t>
   </si>

--- a/output/学生成绩达成度分析.xlsx
+++ b/output/学生成绩达成度分析.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="430" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="860" uniqueCount="13">
   <si>
     <t>考勤</t>
   </si>

--- a/output/学生成绩达成度分析.xlsx
+++ b/output/学生成绩达成度分析.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="860" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="86" uniqueCount="13">
   <si>
     <t>考勤</t>
   </si>

--- a/output/学生成绩达成度分析.xlsx
+++ b/output/学生成绩达成度分析.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="86" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="258" uniqueCount="13">
   <si>
     <t>考勤</t>
   </si>
